--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260727.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260727.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>154,135</t>
+          <t>153,285</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>28.26%</t>
+          <t>28.43%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>17,515</t>
+          <t>17,415</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.53%</t>
+          <t>8.40%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>111,600</t>
+          <t>110,850</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>6.43%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>136,015</t>
+          <t>135,195</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.86%</t>
+          <t>5.81%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>56,815</t>
+          <t>56,475</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.30%</t>
+          <t>5.17%</t>
         </is>
       </c>
     </row>
@@ -721,78 +721,78 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>73,545</t>
+          <t>73,105</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.41%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>6,425</t>
+          <t>66,320</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>50,735</t>
+          <t>6,325</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>66,670</t>
+          <t>50,435</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>22,125</t>
+          <t>21,995</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>20,483</t>
+          <t>20,363</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>35,320</t>
+          <t>35,110</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>22,695</t>
+          <t>22,595</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>86,215</t>
+          <t>85,615</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>57,185</t>
+          <t>56,845</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>21,820</t>
+          <t>21,690</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>29,728</t>
+          <t>29,548</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>40,530</t>
+          <t>40,290</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>66,558</t>
+          <t>66,158</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>23,938</t>
+          <t>23,798</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>8,890</t>
+          <t>8,790</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>142,055</t>
+          <t>141,205</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>13,051</t>
+          <t>12,951</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>20,635</t>
+          <t>20,515</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1139,144 +1139,144 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>10,766</t>
+          <t>10,666</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>69,556,584</t>
+          <t>17,671</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>17,781</t>
+          <t>41,880</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>42,130</t>
+          <t>13,105</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>13,205</t>
+          <t>48,100</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>48,400</t>
+          <t>21,787</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>21,937</t>
+          <t>49,876,688</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,56 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,184,472</t>
+          <t>1,224,092</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.59%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>32,238,000</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>RDI_USD</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>1,290,734</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
